--- a/data/CdS3_1/CdS3_1_IV Graph.xlsx
+++ b/data/CdS3_1/CdS3_1_IV Graph.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{5D120F88-62F2-48CE-8027-5B9E1D67F9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D42BD5A-3F96-4962-96C1-B39ACDACC924}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{C38E384C-E4BC-4AA4-B326-69D77101A4E5}"/>
+    <workbookView minimized="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{C38E384C-E4BC-4AA4-B326-69D77101A4E5}"/>
   </bookViews>
   <sheets>
     <sheet name="CdS3_IV Graph_1" sheetId="1" r:id="rId1"/>
@@ -647,6 +647,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
